--- a/artfynd/S 3124-2023 artfynd.xlsx
+++ b/artfynd/S 3124-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY55"/>
+  <dimension ref="A1:AY56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6942,6 +6942,103 @@
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>135275448</v>
+      </c>
+      <c r="B56" t="n">
+        <v>106311</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>224098</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Kalktallört</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Monotropa hypophegea</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Wallr.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Johannisfors kalkslamdeponi, Upl</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>677347</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6694821</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Forsmark</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 3124-2023 artfynd.xlsx
+++ b/artfynd/S 3124-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY56"/>
+  <dimension ref="A1:AZ56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85521441</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99333314</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1019,6 +1034,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99306856</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1134,6 +1154,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99343578</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1249,6 +1274,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99333310</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1364,6 +1394,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99333330</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1479,6 +1514,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99333306</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1594,6 +1634,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99333312</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1709,6 +1754,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99343584</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1824,6 +1874,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99333307</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1939,6 +1994,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99343583</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2054,6 +2114,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99333332</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2180,6 +2245,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98537423</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2306,6 +2376,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98539440</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2413,6 +2488,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3004584</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2534,6 +2614,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3008787</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2642,6 +2727,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110077702</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2748,6 +2838,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110870838</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2856,6 +2951,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110077091</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2970,6 +3070,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110870796</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3077,6 +3182,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/53941089</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3185,6 +3295,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110077709</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3301,6 +3416,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2709164</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3422,6 +3542,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2715055</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3543,6 +3668,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2715056</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3659,6 +3789,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2716791</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3780,6 +3915,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2719270</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3901,6 +4041,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2719271</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4022,6 +4167,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2719272</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4144,6 +4294,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/53941094</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4265,6 +4420,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/53998061</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4386,6 +4546,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/53998062</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4507,6 +4672,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/53998063</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4628,6 +4798,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/53998065</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4744,6 +4919,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94043569</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4865,6 +5045,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109718443</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4990,6 +5175,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110077089</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5098,6 +5288,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110077699</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5219,6 +5414,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2461290</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5327,6 +5527,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110077756</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5439,6 +5644,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/53941088</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5555,6 +5765,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94043546</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5661,6 +5876,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110870630</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5767,6 +5987,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110870767</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5889,6 +6114,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/53941092</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6011,6 +6241,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/53941093</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6132,6 +6367,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/53998073</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6253,6 +6493,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/53998074</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6369,6 +6614,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5879346</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6485,6 +6735,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5879348</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6601,6 +6856,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/53998064</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6722,6 +6982,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/53998072</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6834,6 +7099,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5900273</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6941,6 +7211,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89805159</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7038,8 +7313,70 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135275448</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 3124-2023 artfynd.xlsx
+++ b/artfynd/S 3124-2023 artfynd.xlsx
@@ -7222,7 +7222,7 @@
         <v>135275448</v>
       </c>
       <c r="B56" t="n">
-        <v>106311</v>
+        <v>106366</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/S 3124-2023 artfynd.xlsx
+++ b/artfynd/S 3124-2023 artfynd.xlsx
@@ -7222,7 +7222,7 @@
         <v>135275448</v>
       </c>
       <c r="B56" t="n">
-        <v>106366</v>
+        <v>106393</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/S 3124-2023 artfynd.xlsx
+++ b/artfynd/S 3124-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ55"/>
+  <dimension ref="A1:AZ56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7214,6 +7214,108 @@
       <c r="AZ55" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/89805159</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>135275448</v>
+      </c>
+      <c r="B56" t="n">
+        <v>106398</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>224098</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Kalktallört</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Monotropa hypophegea</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Wallr.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Johannisfors kalkslamdeponi, Upl</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>677347</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6694821</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Forsmark</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135275448</t>
         </is>
       </c>
     </row>
@@ -7273,6 +7375,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 3124-2023 artfynd.xlsx
+++ b/artfynd/S 3124-2023 artfynd.xlsx
@@ -7222,7 +7222,7 @@
         <v>135275448</v>
       </c>
       <c r="B56" t="n">
-        <v>106398</v>
+        <v>106400</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
